--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78FC2194-236A-4B8D-BAA1-EE64C29F0D00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E65248-FF38-4CDC-83F3-122EC89CA6B8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{449D5468-F607-465B-BAAD-717C894991E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A6A2051-94AE-4106-97C4-71A634AE54F9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98C220C6-6623-4DDB-9BC2-7F03047FC3BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{872E81B5-174B-47D3-A101-7B47F1D961A2}"/>
 </file>
--- a/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
+++ b/deSousa_etal_2009/deSousa_etal_2009_Table1_snapshot.xlsx
@@ -1630,13 +1630,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38E65248-FF38-4CDC-83F3-122EC89CA6B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53F7AB64-C673-43FF-A0DD-D9FDD91E0C9B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A6A2051-94AE-4106-97C4-71A634AE54F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29DA1EEA-87BA-48D2-804E-68DE25BF204E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{872E81B5-174B-47D3-A101-7B47F1D961A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F03075-165C-425F-B677-3B085EB33D6A}"/>
 </file>